--- a/training_forms/031_mental_health_first_aid_training_enrollment_form--training_forms.xlsx
+++ b/training_forms/031_mental_health_first_aid_training_enrollment_form--training_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -642,8 +642,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -671,12 +671,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'session_date',_'label':_'session_date',_'hint':_none,_'type':_'date',_'options':_[]}</t>
+          <t>session_date</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'session_date', 'label': 'Session Date', 'hint': None, 'type': 'date', 'options': []}</t>
+          <t>Session Date</t>
         </is>
       </c>
     </row>
@@ -688,12 +688,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'session_time',_'label':_'session_time',_'hint':_none,_'type':_'time',_'options':_[]}</t>
+          <t>session_time</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'session_time', 'label': 'Session Time', 'hint': None, 'type': 'time', 'options': []}</t>
+          <t>Session Time</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'session_duration',_'label':_'session_duration',_'hint':_none,_'type':_'integer',_'options':_[]}</t>
+          <t>session_duration</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'session_duration', 'label': 'Session Duration', 'hint': None, 'type': 'integer', 'options': []}</t>
+          <t>Session Duration</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'participant_status_option_1',_'label':_'not_started',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'participant_status_option_1', 'label': 'Not Started', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -739,12 +739,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'participant_status_option_2',_'label':_'in_progress',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'participant_status_option_2', 'label': 'In Progress', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -756,12 +756,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'participant_status_option_3',_'label':_'completed',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'participant_status_option_3', 'label': 'Completed', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
